--- a/mode_docx_gen/modes2/БНТ_8.xlsx
+++ b/mode_docx_gen/modes2/БНТ_8.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28725" windowHeight="10815"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28725" windowHeight="10815" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SGF_Parameters" sheetId="1" r:id="rId1"/>
@@ -210,24 +210,6 @@
     <t>Ratio_phar1_lvttoc</t>
   </si>
   <si>
-    <t>u_min_lvrbvtr1</t>
-  </si>
-  <si>
-    <t>u2_max_lvrbvtr1</t>
-  </si>
-  <si>
-    <t>t1_lvrbvtr1</t>
-  </si>
-  <si>
-    <t>u_min_lvrbvtr2</t>
-  </si>
-  <si>
-    <t>u2_max_lvrbvtr2</t>
-  </si>
-  <si>
-    <t>t1_lvrbvtr2</t>
-  </si>
-  <si>
     <t>VYVOD</t>
   </si>
   <si>
@@ -541,6 +523,24 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>Umin_lvrbvtr1</t>
+  </si>
+  <si>
+    <t>U2max_lvrbvtr1</t>
+  </si>
+  <si>
+    <t>T1_lvrbvtr1</t>
+  </si>
+  <si>
+    <t>Umin_lvrbvtr2</t>
+  </si>
+  <si>
+    <t>U2max_lvrbvtr2</t>
+  </si>
+  <si>
+    <t>T1_lvrbvtr2</t>
   </si>
 </sst>
 </file>
@@ -1262,22 +1262,22 @@
         <v>61</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -1360,121 +1360,121 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.25">
@@ -1611,390 +1611,390 @@
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="O2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="P2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="Q2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="R2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="S2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="T2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="U2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="V2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="W2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="Y2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="Z2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AA2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AB2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AD2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AE2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AG2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AH2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AI2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AJ2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AK2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AL2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AM2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AN2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AO2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AP2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AQ2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AR2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AS2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AT2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AU2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AW2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AX2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AZ2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BA2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BB2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BC2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BD2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BE2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BF2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BG2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BH2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BI2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BJ2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BK2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="BL2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
